--- a/data/trans_orig/P21-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2007</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>377286</t>
+          <t>377841</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>409882</t>
+          <t>410868</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>222643</t>
+          <t>222820</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>250812</t>
+          <t>252097</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>612114</t>
+          <t>609976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>654920</t>
+          <t>654725</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,89%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>10235</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11920</t>
+          <t>11366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61208</t>
+          <t>59231</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94161</t>
+          <t>90880</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55003</t>
+          <t>53689</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83182</t>
+          <t>83078</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>122346</t>
+          <t>121888</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>164730</t>
+          <t>165633</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>282156</t>
+          <t>281342</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>313768</t>
+          <t>314624</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>262998</t>
+          <t>263594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>296816</t>
+          <t>294950</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>557058</t>
+          <t>556020</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>600944</t>
+          <t>600727</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,42 +1357,42 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>4820</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>1741</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>11255</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>1,53%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>4820</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1724</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>10913</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49023</t>
+          <t>49245</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80634</t>
+          <t>81264</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72943</t>
+          <t>74812</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105978</t>
+          <t>105658</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>132080</t>
+          <t>133686</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175324</t>
+          <t>175459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>427322</t>
+          <t>428905</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>462983</t>
+          <t>463350</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108026</t>
+          <t>107657</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>131177</t>
+          <t>131768</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>545576</t>
+          <t>543761</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>586747</t>
+          <t>587079</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78208</t>
+          <t>78146</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113976</t>
+          <t>113057</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34761</t>
+          <t>33659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57311</t>
+          <t>57582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>121205</t>
+          <t>121146</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>161715</t>
+          <t>165115</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>984675</t>
+          <t>985758</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1040379</t>
+          <t>1043407</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>503896</t>
+          <t>501908</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>550804</t>
+          <t>547368</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1500364</t>
+          <t>1502924</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1570827</t>
+          <t>1574976</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15725</t>
+          <t>14671</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16463</t>
+          <t>16713</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25517</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>191563</t>
+          <t>185010</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>246027</t>
+          <t>244330</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>156237</t>
+          <t>158022</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>201546</t>
+          <t>203062</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>364216</t>
+          <t>361523</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>435389</t>
+          <t>431617</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287093</t>
+          <t>287188</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>313956</t>
+          <t>313061</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>408526</t>
+          <t>410991</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>450450</t>
+          <t>453533</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>708398</t>
+          <t>706793</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>758894</t>
+          <t>757912</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,44%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12985</t>
+          <t>13312</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>16216</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34183</t>
+          <t>35285</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59896</t>
+          <t>60142</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>111475</t>
+          <t>110523</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>153318</t>
+          <t>152348</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>153273</t>
+          <t>153472</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>201798</t>
+          <t>203947</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>240436</t>
+          <t>240167</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>264652</t>
+          <t>264192</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>927710</t>
+          <t>925535</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>986454</t>
+          <t>987203</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1176568</t>
+          <t>1178062</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1240220</t>
+          <t>1241103</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,23%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>9300</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26314</t>
+          <t>26386</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10653</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28631</t>
+          <t>28712</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32517</t>
+          <t>32058</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>56298</t>
+          <t>55919</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>246836</t>
+          <t>246152</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>303797</t>
+          <t>307737</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>289409</t>
+          <t>289921</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>353044</t>
+          <t>353487</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2664050</t>
+          <t>2667416</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2752392</t>
+          <t>2752762</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2502665</t>
+          <t>2499682</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2602699</t>
+          <t>2599707</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5192910</t>
+          <t>5196369</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5322092</t>
+          <t>5330532</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,2%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12408</t>
+          <t>11861</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31139</t>
+          <t>30510</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25733</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49461</t>
+          <t>49892</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41780</t>
+          <t>41646</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>70648</t>
+          <t>71574</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>497437</t>
+          <t>498025</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>585883</t>
+          <t>582194</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>740684</t>
+          <t>746276</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>836731</t>
+          <t>842282</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1269706</t>
+          <t>1262444</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397915</t>
+          <t>1393132</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2012</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>365999</t>
+          <t>364754</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>394872</t>
+          <t>396238</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>214621</t>
+          <t>214965</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>248372</t>
+          <t>250282</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>592656</t>
+          <t>592811</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>637122</t>
+          <t>635589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,56%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40255</t>
+          <t>39713</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68091</t>
+          <t>70716</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64786</t>
+          <t>63834</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>98892</t>
+          <t>98175</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112268</t>
+          <t>113052</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>156460</t>
+          <t>156008</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>330306</t>
+          <t>329736</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362597</t>
+          <t>362713</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>232480</t>
+          <t>231044</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>264632</t>
+          <t>265408</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>572007</t>
+          <t>568829</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>618762</t>
+          <t>618983</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>958</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9534</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54232</t>
+          <t>54402</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85781</t>
+          <t>86404</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69836</t>
+          <t>68560</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>101976</t>
+          <t>102531</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>132236</t>
+          <t>131916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>179642</t>
+          <t>181197</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>448315</t>
+          <t>446465</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>494058</t>
+          <t>493722</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>191677</t>
+          <t>194047</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>217924</t>
+          <t>220346</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>651511</t>
+          <t>650458</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>703660</t>
+          <t>703971</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,22%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>15085</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18795</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127254</t>
+          <t>127693</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>171900</t>
+          <t>174321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39791</t>
+          <t>37710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65514</t>
+          <t>63317</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>174673</t>
+          <t>175097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227346</t>
+          <t>228540</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>871138</t>
+          <t>872125</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>928194</t>
+          <t>931974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>516294</t>
+          <t>518962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>569042</t>
+          <t>571118</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1408966</t>
+          <t>1408980</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1485342</t>
+          <t>1488875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22177</t>
+          <t>21440</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>16870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>13336</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33583</t>
+          <t>32839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>215362</t>
+          <t>212011</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>273144</t>
+          <t>270676</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>189576</t>
+          <t>187380</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>241678</t>
+          <t>239949</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>418648</t>
+          <t>416773</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>495973</t>
+          <t>491217</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>382274</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>420455</t>
+          <t>419120</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>503211</t>
+          <t>501496</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>552102</t>
+          <t>553701</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>897692</t>
+          <t>896334</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>962264</t>
+          <t>963167</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,77%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22018</t>
+          <t>21975</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14286</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>32238</t>
+          <t>33376</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>82227</t>
+          <t>84521</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>118811</t>
+          <t>120513</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>197021</t>
+          <t>194305</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>246383</t>
+          <t>247805</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>287621</t>
+          <t>288199</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>351230</t>
+          <t>351472</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>192443</t>
+          <t>190704</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>220378</t>
+          <t>219435</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>777247</t>
+          <t>777511</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>838432</t>
+          <t>839438</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>979439</t>
+          <t>976601</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1043536</t>
+          <t>1045693</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,98%</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17617</t>
+          <t>16928</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40298</t>
+          <t>38877</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19284</t>
+          <t>19577</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40287</t>
+          <t>41091</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44237</t>
+          <t>45833</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>73306</t>
+          <t>73521</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>247237</t>
+          <t>244713</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>305976</t>
+          <t>302616</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>304304</t>
+          <t>302343</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>366957</t>
+          <t>367756</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2661750</t>
+          <t>2663188</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2758449</t>
+          <t>2761581</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2517063</t>
+          <t>2514169</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2627359</t>
+          <t>2619455</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5200422</t>
+          <t>5205193</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5346438</t>
+          <t>5357079</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,9%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24299</t>
+          <t>25075</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48454</t>
+          <t>48997</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>40048</t>
+          <t>40185</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69305</t>
+          <t>69718</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>70518</t>
+          <t>69319</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>109444</t>
+          <t>108451</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>624900</t>
+          <t>622173</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>720755</t>
+          <t>717777</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>870048</t>
+          <t>875346</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>974233</t>
+          <t>981848</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1533747</t>
+          <t>1524924</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1677206</t>
+          <t>1669083</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2016</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2016 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>348918</t>
+          <t>347394</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>380255</t>
+          <t>379611</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>252394</t>
+          <t>250452</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>282096</t>
+          <t>282398</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>611321</t>
+          <t>609992</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>655311</t>
+          <t>653071</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,44%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15481</t>
+          <t>15151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19953</t>
+          <t>20133</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45793</t>
+          <t>46087</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76146</t>
+          <t>78014</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55205</t>
+          <t>55529</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>84397</t>
+          <t>85052</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>109313</t>
+          <t>108736</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152229</t>
+          <t>151447</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>304783</t>
+          <t>304807</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>332720</t>
+          <t>333611</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>273148</t>
+          <t>272859</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305227</t>
+          <t>305779</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>586431</t>
+          <t>587607</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>629226</t>
+          <t>629682</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,33%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>983</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10116</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14193</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39252</t>
+          <t>38630</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65773</t>
+          <t>66397</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63337</t>
+          <t>61572</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94618</t>
+          <t>93993</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110358</t>
+          <t>109720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153063</t>
+          <t>151560</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>412685</t>
+          <t>412784</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>449842</t>
+          <t>449255</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>122014</t>
+          <t>122176</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>143557</t>
+          <t>142322</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>543518</t>
+          <t>543182</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>583586</t>
+          <t>584265</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12957</t>
+          <t>13543</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>8402</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17186</t>
+          <t>18082</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66429</t>
+          <t>66714</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102557</t>
+          <t>101652</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19402</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39994</t>
+          <t>39269</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94425</t>
+          <t>92860</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135855</t>
+          <t>133183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>927723</t>
+          <t>928092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>980555</t>
+          <t>977666</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>601566</t>
+          <t>599051</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>650320</t>
+          <t>650645</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1541488</t>
+          <t>1543990</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1612465</t>
+          <t>1614525</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,92%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26298</t>
+          <t>25927</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20401</t>
+          <t>20385</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18043</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40444</t>
+          <t>39671</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>151117</t>
+          <t>151436</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>199933</t>
+          <t>200290</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164540</t>
+          <t>165402</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>212527</t>
+          <t>214880</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>331372</t>
+          <t>331289</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>398789</t>
+          <t>399274</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>498355</t>
+          <t>497110</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>535895</t>
+          <t>532702</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>561971</t>
+          <t>561425</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>607483</t>
+          <t>608790</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1073489</t>
+          <t>1072096</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1132697</t>
+          <t>1132751</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20672</t>
+          <t>21358</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25604</t>
+          <t>25732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20064</t>
+          <t>20367</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>41557</t>
+          <t>42739</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68453</t>
+          <t>70959</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>102964</t>
+          <t>104288</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>116597</t>
+          <t>115664</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>161094</t>
+          <t>161087</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>194676</t>
+          <t>196522</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>251611</t>
+          <t>252052</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>208108</t>
+          <t>207268</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>235985</t>
+          <t>236316</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>830545</t>
+          <t>833296</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>886182</t>
+          <t>889526</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1054988</t>
+          <t>1052844</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1116049</t>
+          <t>1112860</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,36%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9998,7 +9998,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11908</t>
+          <t>11399</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31495</t>
+          <t>31644</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35082</t>
+          <t>34353</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47452</t>
+          <t>48347</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>75153</t>
+          <t>77392</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>173363</t>
+          <t>170140</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>227199</t>
+          <t>223755</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>230366</t>
+          <t>231095</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>287292</t>
+          <t>289324</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2765276</t>
+          <t>2765453</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2854668</t>
+          <t>2853959</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2714653</t>
+          <t>2712471</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2817011</t>
+          <t>2809431</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5500729</t>
+          <t>5506958</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5639112</t>
+          <t>5640801</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,75%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>34053</t>
+          <t>33960</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>61694</t>
+          <t>61464</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>45883</t>
+          <t>46395</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>79531</t>
+          <t>77939</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>87074</t>
+          <t>87858</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>129332</t>
+          <t>128593</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>479804</t>
+          <t>479661</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>561009</t>
+          <t>563636</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>651859</t>
+          <t>656848</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>747391</t>
+          <t>755040</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1152375</t>
+          <t>1152278</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1288644</t>
+          <t>1282322</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2023</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año por un problema o enfermedad propio en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>359205</t>
+          <t>357110</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>401409</t>
+          <t>400326</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>321754</t>
+          <t>321839</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>353318</t>
+          <t>352159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>691418</t>
+          <t>691577</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>745408</t>
+          <t>743013</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,19%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11361</t>
+          <t>10740</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9294</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15588</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97043</t>
+          <t>97574</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>138339</t>
+          <t>138993</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>88865</t>
+          <t>90955</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120716</t>
+          <t>120874</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>197380</t>
+          <t>197955</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>250470</t>
+          <t>248161</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357085</t>
+          <t>357321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>389034</t>
+          <t>389958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>266389</t>
+          <t>266316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>296467</t>
+          <t>295952</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>633250</t>
+          <t>636881</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>679941</t>
+          <t>679745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63179</t>
+          <t>62255</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95128</t>
+          <t>94892</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81276</t>
+          <t>82591</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111007</t>
+          <t>111962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150906</t>
+          <t>150737</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198768</t>
+          <t>194986</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>523090</t>
+          <t>520525</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>636870</t>
+          <t>634568</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>103311</t>
+          <t>103079</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>123190</t>
+          <t>123057</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>625864</t>
+          <t>628540</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>771380</t>
+          <t>779094</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>289</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30923</t>
+          <t>32525</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143034</t>
+          <t>144070</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42599</t>
+          <t>42513</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62414</t>
+          <t>62332</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63159</t>
+          <t>54012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>205203</t>
+          <t>202883</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>776508</t>
+          <t>774824</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>836618</t>
+          <t>835784</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>282256</t>
+          <t>334254</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>709691</t>
+          <t>712191</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>979161</t>
+          <t>920719</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1532744</t>
+          <t>1530347</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,03%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>11561</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>10859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18523</t>
+          <t>18528</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>192366</t>
+          <t>192785</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>252316</t>
+          <t>253111</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>262159</t>
+          <t>259043</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>695957</t>
+          <t>641995</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>467557</t>
+          <t>470287</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1027161</t>
+          <t>1086753</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>53,99%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>358085</t>
+          <t>356961</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>394773</t>
+          <t>394003</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>631814</t>
+          <t>631308</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>706560</t>
+          <t>706788</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1007612</t>
+          <t>1005630</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1088559</t>
+          <t>1085987</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,68%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>11744</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>19685</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74222</t>
+          <t>75593</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>109240</t>
+          <t>111428</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>127414</t>
+          <t>129009</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>200629</t>
+          <t>200971</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>216404</t>
+          <t>216473</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>294343</t>
+          <t>295824</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>171004</t>
+          <t>167404</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>210896</t>
+          <t>211535</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>573633</t>
+          <t>578005</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>617471</t>
+          <t>618476</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>758954</t>
+          <t>756107</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>817387</t>
+          <t>819683</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -13409,7 +13409,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15368</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28321</t>
+          <t>28146</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68854</t>
+          <t>71572</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>131411</t>
+          <t>131146</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>175690</t>
+          <t>172173</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>171354</t>
+          <t>170191</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>229821</t>
+          <t>231936</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2643576</t>
+          <t>2647857</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2852612</t>
+          <t>2854360</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2004491</t>
+          <t>2037602</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2723491</t>
+          <t>2723027</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4645815</t>
+          <t>4686159</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5476757</t>
+          <t>5478154</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,89%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29788</t>
+          <t>29002</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20414</t>
+          <t>19804</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>38912</t>
+          <t>37426</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>36344</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60471</t>
+          <t>60158</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>506041</t>
+          <t>504687</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>708597</t>
+          <t>705650</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>816973</t>
+          <t>816181</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1537449</t>
+          <t>1505589</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1420503</t>
+          <t>1418450</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2266685</t>
+          <t>2218265</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>377841</t>
+          <t>377397</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>410868</t>
+          <t>412130</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>222820</t>
+          <t>222843</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>252097</t>
+          <t>252450</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>609976</t>
+          <t>612142</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>654725</t>
+          <t>656830</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>9948</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11743</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59231</t>
+          <t>58860</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90880</t>
+          <t>91261</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53689</t>
+          <t>53545</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83078</t>
+          <t>83381</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>121888</t>
+          <t>120835</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>165633</t>
+          <t>164781</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>281342</t>
+          <t>283369</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>314624</t>
+          <t>313884</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>263594</t>
+          <t>263068</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>294950</t>
+          <t>296935</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>556020</t>
+          <t>553320</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>600727</t>
+          <t>600024</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11255</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49245</t>
+          <t>49324</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81264</t>
+          <t>80042</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74812</t>
+          <t>73073</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105658</t>
+          <t>107402</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133686</t>
+          <t>133705</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175459</t>
+          <t>179876</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>428905</t>
+          <t>427175</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>463350</t>
+          <t>461338</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>107657</t>
+          <t>109412</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>131768</t>
+          <t>132534</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>543761</t>
+          <t>544311</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>587079</t>
+          <t>587606</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,74%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>895</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8286</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78146</t>
+          <t>79544</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113057</t>
+          <t>114269</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33659</t>
+          <t>33529</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57582</t>
+          <t>56511</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>121146</t>
+          <t>119783</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165115</t>
+          <t>162414</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>985758</t>
+          <t>984743</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1043407</t>
+          <t>1039975</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>501908</t>
+          <t>501404</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>547368</t>
+          <t>546806</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1502924</t>
+          <t>1502077</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1574976</t>
+          <t>1572632</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,54%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14671</t>
+          <t>14797</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16713</t>
+          <t>17672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26628</t>
+          <t>25873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>185010</t>
+          <t>192705</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>244330</t>
+          <t>245304</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>158022</t>
+          <t>158136</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203062</t>
+          <t>202349</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>361523</t>
+          <t>364363</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>431617</t>
+          <t>435539</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287188</t>
+          <t>287902</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>313061</t>
+          <t>315017</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>410991</t>
+          <t>409853</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>453533</t>
+          <t>453883</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>706793</t>
+          <t>708371</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>757912</t>
+          <t>757113</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,36%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13312</t>
+          <t>12810</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16216</t>
+          <t>15962</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35285</t>
+          <t>33721</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60142</t>
+          <t>59418</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>110523</t>
+          <t>110345</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>152348</t>
+          <t>152922</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>153472</t>
+          <t>154703</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>203947</t>
+          <t>202801</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>240167</t>
+          <t>240569</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>264192</t>
+          <t>265918</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>925535</t>
+          <t>928301</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>987203</t>
+          <t>986694</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1178062</t>
+          <t>1179602</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1241103</t>
+          <t>1242136</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,3%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26386</t>
+          <t>25848</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28712</t>
+          <t>28739</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32058</t>
+          <t>31449</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55919</t>
+          <t>56123</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>246152</t>
+          <t>247925</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>307737</t>
+          <t>304075</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>289921</t>
+          <t>286867</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>353487</t>
+          <t>349908</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2667416</t>
+          <t>2668594</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2752762</t>
+          <t>2751557</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2499682</t>
+          <t>2507472</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2599707</t>
+          <t>2603430</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5196369</t>
+          <t>5194240</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5330532</t>
+          <t>5330136</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,19%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11861</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30510</t>
+          <t>29911</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24584</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>49892</t>
+          <t>48169</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41646</t>
+          <t>40482</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71574</t>
+          <t>72377</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>498025</t>
+          <t>498827</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>582194</t>
+          <t>583621</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>746276</t>
+          <t>740554</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>842282</t>
+          <t>834536</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1262444</t>
+          <t>1263737</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1393132</t>
+          <t>1396594</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>364754</t>
+          <t>366382</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>396238</t>
+          <t>395682</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>214965</t>
+          <t>215601</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>250282</t>
+          <t>250117</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>592811</t>
+          <t>592232</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>635589</t>
+          <t>637678</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>945</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39713</t>
+          <t>39991</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70716</t>
+          <t>68971</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63834</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>98175</t>
+          <t>97794</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>113052</t>
+          <t>110870</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>156008</t>
+          <t>157257</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>329736</t>
+          <t>329691</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362713</t>
+          <t>362536</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>231044</t>
+          <t>232150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>265408</t>
+          <t>266400</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>568829</t>
+          <t>572332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>618983</t>
+          <t>619541</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,1%</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6408</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>961</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>8729</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54402</t>
+          <t>54275</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86404</t>
+          <t>87254</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68560</t>
+          <t>68335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102531</t>
+          <t>102415</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131916</t>
+          <t>131543</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181197</t>
+          <t>178731</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>446465</t>
+          <t>448110</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>493722</t>
+          <t>494511</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>194047</t>
+          <t>192556</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>220346</t>
+          <t>219059</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>650458</t>
+          <t>652770</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>703971</t>
+          <t>703068</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>14127</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>890</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8190</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17820</t>
+          <t>19246</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>127693</t>
+          <t>127119</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>174321</t>
+          <t>172776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37710</t>
+          <t>37933</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63317</t>
+          <t>64006</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>175097</t>
+          <t>175806</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>228540</t>
+          <t>225007</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>872125</t>
+          <t>873384</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>931974</t>
+          <t>931549</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>518962</t>
+          <t>521122</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>571118</t>
+          <t>570416</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1408980</t>
+          <t>1405843</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1488875</t>
+          <t>1485406</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,21%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21440</t>
+          <t>21064</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16870</t>
+          <t>17182</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>13408</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32839</t>
+          <t>31864</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>212011</t>
+          <t>214152</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>270676</t>
+          <t>270764</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>187380</t>
+          <t>188192</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>239949</t>
+          <t>237883</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>416773</t>
+          <t>420089</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>491217</t>
+          <t>497342</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>382274</t>
+          <t>383251</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>419120</t>
+          <t>417756</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>501496</t>
+          <t>502140</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>553701</t>
+          <t>555654</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>896334</t>
+          <t>895189</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>963167</t>
+          <t>960130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,53%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>17094</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21975</t>
+          <t>21540</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13410</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33376</t>
+          <t>32480</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84521</t>
+          <t>83433</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>120513</t>
+          <t>117074</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>194305</t>
+          <t>193597</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>247805</t>
+          <t>246847</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>288199</t>
+          <t>289616</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>351472</t>
+          <t>352572</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>190704</t>
+          <t>193219</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>219435</t>
+          <t>219553</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>777511</t>
+          <t>772728</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>839438</t>
+          <t>835808</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>976601</t>
+          <t>980350</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1045693</t>
+          <t>1047642</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,12%</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16928</t>
+          <t>18129</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38877</t>
+          <t>39173</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19577</t>
+          <t>19425</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41091</t>
+          <t>40386</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45833</t>
+          <t>45613</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>73521</t>
+          <t>71597</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>244713</t>
+          <t>247895</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>302616</t>
+          <t>306319</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>302343</t>
+          <t>300568</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>367756</t>
+          <t>367447</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2663188</t>
+          <t>2661626</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2761581</t>
+          <t>2760482</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2514169</t>
+          <t>2511949</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2619455</t>
+          <t>2620563</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5205193</t>
+          <t>5206237</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5357079</t>
+          <t>5347069</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25075</t>
+          <t>24515</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48997</t>
+          <t>48220</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>40185</t>
+          <t>40507</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69718</t>
+          <t>69984</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>69319</t>
+          <t>72190</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>108451</t>
+          <t>108354</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>622173</t>
+          <t>622997</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>717777</t>
+          <t>721516</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>875346</t>
+          <t>875294</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>981848</t>
+          <t>982838</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1524924</t>
+          <t>1533719</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1669083</t>
+          <t>1672908</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>347394</t>
+          <t>348602</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>379611</t>
+          <t>380269</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>250452</t>
+          <t>251972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>282398</t>
+          <t>283461</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>609992</t>
+          <t>609591</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>653071</t>
+          <t>653445</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>15052</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20133</t>
+          <t>19210</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46087</t>
+          <t>45840</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78014</t>
+          <t>77243</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55529</t>
+          <t>53619</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85052</t>
+          <t>83416</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>108736</t>
+          <t>110050</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>151447</t>
+          <t>151910</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>304807</t>
+          <t>303596</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>333611</t>
+          <t>332983</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>272859</t>
+          <t>270141</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305779</t>
+          <t>303749</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>587607</t>
+          <t>585925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>629682</t>
+          <t>628088</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,12%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>9350</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15139</t>
+          <t>14708</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38630</t>
+          <t>39347</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66397</t>
+          <t>67351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61572</t>
+          <t>62974</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93993</t>
+          <t>97250</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109720</t>
+          <t>110539</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151560</t>
+          <t>152398</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>412784</t>
+          <t>412353</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>449255</t>
+          <t>448197</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>122176</t>
+          <t>121614</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>142322</t>
+          <t>141535</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>543182</t>
+          <t>545784</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>584265</t>
+          <t>585078</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,24%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13543</t>
+          <t>15093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18082</t>
+          <t>17021</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66714</t>
+          <t>68259</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101652</t>
+          <t>102712</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>20644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39269</t>
+          <t>40587</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92860</t>
+          <t>93948</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>133183</t>
+          <t>131996</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>928092</t>
+          <t>926492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>977666</t>
+          <t>978736</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>599051</t>
+          <t>597965</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>650645</t>
+          <t>648224</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1543990</t>
+          <t>1540000</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1614525</t>
+          <t>1612904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25927</t>
+          <t>26385</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20385</t>
+          <t>21758</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>18107</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39671</t>
+          <t>40495</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>151436</t>
+          <t>151141</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>200290</t>
+          <t>201507</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>165402</t>
+          <t>167285</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>214880</t>
+          <t>215236</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>331289</t>
+          <t>331399</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>399274</t>
+          <t>399922</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>497110</t>
+          <t>495477</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>532702</t>
+          <t>533700</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>561425</t>
+          <t>564668</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>608790</t>
+          <t>609745</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1072096</t>
+          <t>1071976</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1132751</t>
+          <t>1132881</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,62%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21358</t>
+          <t>22553</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25732</t>
+          <t>24826</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20367</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42739</t>
+          <t>40231</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70959</t>
+          <t>70719</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104288</t>
+          <t>107349</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>115664</t>
+          <t>114384</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>161087</t>
+          <t>158369</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>196522</t>
+          <t>195570</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>252052</t>
+          <t>252918</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>207268</t>
+          <t>208614</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>236316</t>
+          <t>238510</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>833296</t>
+          <t>835495</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>889526</t>
+          <t>887178</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1052844</t>
+          <t>1051114</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1112860</t>
+          <t>1115830</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11399</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31644</t>
+          <t>32786</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13457</t>
+          <t>13603</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34353</t>
+          <t>34920</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>48347</t>
+          <t>46968</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77392</t>
+          <t>76126</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>170140</t>
+          <t>173769</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>223755</t>
+          <t>225876</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>231095</t>
+          <t>230080</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>289324</t>
+          <t>294122</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2765453</t>
+          <t>2764848</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2853959</t>
+          <t>2853117</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2712471</t>
+          <t>2710196</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2809431</t>
+          <t>2814152</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5506958</t>
+          <t>5501932</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5640801</t>
+          <t>5639210</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>33960</t>
+          <t>33663</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>61464</t>
+          <t>61743</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>46395</t>
+          <t>45511</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>77939</t>
+          <t>79397</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>87858</t>
+          <t>86509</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>128593</t>
+          <t>131210</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>479661</t>
+          <t>480250</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>563636</t>
+          <t>564725</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>656848</t>
+          <t>655520</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>755040</t>
+          <t>752502</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1152278</t>
+          <t>1153523</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1282322</t>
+          <t>1289509</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>382022</t>
+          <t>417897</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>357110</t>
+          <t>394136</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>400326</t>
+          <t>437200</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>337683</t>
+          <t>369702</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>321839</t>
+          <t>354109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>352159</t>
+          <t>386537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>719706</t>
+          <t>787598</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>691577</t>
+          <t>759158</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>743013</t>
+          <t>813460</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,5%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>11247</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10174</t>
+          <t>10276</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16479</t>
+          <t>17279</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>116330</t>
+          <t>125478</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97574</t>
+          <t>106095</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>138993</t>
+          <t>149587</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>105581</t>
+          <t>113754</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90955</t>
+          <t>96982</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120874</t>
+          <t>129019</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>221910</t>
+          <t>239232</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>197955</t>
+          <t>211928</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>248161</t>
+          <t>267686</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>503459</t>
+          <t>548648</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>503459</t>
+          <t>548648</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>503459</t>
+          <t>548648</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>446750</t>
+          <t>487663</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>446750</t>
+          <t>487663</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>446750</t>
+          <t>487663</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>950209</t>
+          <t>1036310</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>950209</t>
+          <t>1036310</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>950209</t>
+          <t>1036310</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>374680</t>
+          <t>400990</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357321</t>
+          <t>382087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>389958</t>
+          <t>416923</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>282906</t>
+          <t>313111</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>266316</t>
+          <t>295104</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>295952</t>
+          <t>328550</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>657585</t>
+          <t>714100</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>636881</t>
+          <t>687826</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>679745</t>
+          <t>735908</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,27%</t>
         </is>
       </c>
     </row>
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>8754</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>77533</t>
+          <t>82222</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62255</t>
+          <t>66289</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94892</t>
+          <t>101125</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>95314</t>
+          <t>104956</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82591</t>
+          <t>89354</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111962</t>
+          <t>122076</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>172847</t>
+          <t>187179</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150737</t>
+          <t>165094</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194986</t>
+          <t>213600</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>381705</t>
+          <t>422270</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>381705</t>
+          <t>422270</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>381705</t>
+          <t>422270</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>833917</t>
+          <t>905482</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>833917</t>
+          <t>905482</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>833917</t>
+          <t>905482</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>580727</t>
+          <t>374885</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>520525</t>
+          <t>355037</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>634568</t>
+          <t>392821</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,27 +11953,27 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>113983</t>
+          <t>127973</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>103079</t>
+          <t>115611</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>123057</t>
+          <t>138257</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>694710</t>
+          <t>502858</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>628540</t>
+          <t>479816</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>779094</t>
+          <t>521619</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>79,22%</t>
         </is>
       </c>
     </row>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -12041,12 +12041,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -12056,77 +12056,77 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2289</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6461</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>0,98%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2351</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6554</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>86000</t>
+          <t>95019</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32525</t>
+          <t>77142</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144070</t>
+          <t>114962</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51816</t>
+          <t>58345</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42513</t>
+          <t>48168</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62332</t>
+          <t>70968</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>137816</t>
+          <t>153364</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54012</t>
+          <t>134159</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>202883</t>
+          <t>175824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166260</t>
+          <t>186805</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166260</t>
+          <t>186805</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166260</t>
+          <t>186805</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>834524</t>
+          <t>658416</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>834524</t>
+          <t>658416</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>834524</t>
+          <t>658416</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>808189</t>
+          <t>881335</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>774824</t>
+          <t>848498</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>835784</t>
+          <t>910151</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>555558</t>
+          <t>615913</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>334254</t>
+          <t>591851</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>712191</t>
+          <t>639323</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1363746</t>
+          <t>1497248</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>920719</t>
+          <t>1456320</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1530347</t>
+          <t>1531054</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -12487,27 +12487,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>11649</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>11325</t>
+          <t>12147</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18528</t>
+          <t>18816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>220540</t>
+          <t>244333</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>192785</t>
+          <t>215316</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>253111</t>
+          <t>278001</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>417301</t>
+          <t>239326</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>259043</t>
+          <t>217365</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>641995</t>
+          <t>264027</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>637841</t>
+          <t>483659</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>470287</t>
+          <t>449943</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1086753</t>
+          <t>525621</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>378502</t>
+          <t>458623</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>356961</t>
+          <t>435574</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>394003</t>
+          <t>476627</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>661243</t>
+          <t>630338</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>631308</t>
+          <t>607463</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>706788</t>
+          <t>649126</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1039745</t>
+          <t>1088960</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1005630</t>
+          <t>1058077</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1085987</t>
+          <t>1115716</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>79,83%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>13295</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9891</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>11288</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>7727</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19685</t>
+          <t>20890</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>90671</t>
+          <t>102579</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75593</t>
+          <t>84726</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111428</t>
+          <t>125611</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>171792</t>
+          <t>193241</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>129009</t>
+          <t>174568</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>200971</t>
+          <t>215324</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>262463</t>
+          <t>295819</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>216473</t>
+          <t>269097</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>295824</t>
+          <t>325984</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>838450</t>
+          <t>829583</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>838450</t>
+          <t>829583</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>838450</t>
+          <t>829583</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1313496</t>
+          <t>1397546</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1313496</t>
+          <t>1397546</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1313496</t>
+          <t>1397546</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,32 +13286,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>194444</t>
+          <t>194851</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>167404</t>
+          <t>173801</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>211535</t>
+          <t>210418</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>597720</t>
+          <t>666253</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>578005</t>
+          <t>642241</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>618476</t>
+          <t>686812</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>792165</t>
+          <t>861103</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>756107</t>
+          <t>830042</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>819683</t>
+          <t>890737</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,58%</t>
         </is>
       </c>
     </row>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>812</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,17 +13434,17 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>10668</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15194</t>
+          <t>16596</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>10487</t>
+          <t>11480</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16120</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -13512,32 +13512,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>45203</t>
+          <t>41566</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28146</t>
+          <t>25877</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>71572</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>151265</t>
+          <t>164543</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>131146</t>
+          <t>143871</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>172173</t>
+          <t>187697</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>196468</t>
+          <t>206108</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>170191</t>
+          <t>178600</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>231936</t>
+          <t>237768</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>758612</t>
+          <t>841464</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>758612</t>
+          <t>841464</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>758612</t>
+          <t>841464</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>999120</t>
+          <t>1078692</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>999120</t>
+          <t>1078692</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>999120</t>
+          <t>1078692</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2718564</t>
+          <t>2728579</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2647857</t>
+          <t>2675421</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2854360</t>
+          <t>2778806</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2549093</t>
+          <t>2723289</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2037602</t>
+          <t>2675250</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2723027</t>
+          <t>2768523</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5267656</t>
+          <t>5451869</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4686159</t>
+          <t>5376117</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5478154</t>
+          <t>5517649</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,05%</t>
         </is>
       </c>
     </row>
@@ -13855,102 +13855,102 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>19467</t>
+          <t>20730</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12178</t>
+          <t>14046</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29002</t>
+          <t>30504</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>31541</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>22918</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>41875</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>52271</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>40778</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>66104</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>27709</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>19804</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>37426</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>47177</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>36231</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>60158</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>636276</t>
+          <t>691196</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>504687</t>
+          <t>639488</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>705650</t>
+          <t>742969</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>993069</t>
+          <t>874166</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>816181</t>
+          <t>829357</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1505589</t>
+          <t>921047</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1629345</t>
+          <t>1565362</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1418450</t>
+          <t>1500863</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2218265</t>
+          <t>1638622</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3374307</t>
+          <t>3440505</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3374307</t>
+          <t>3440505</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3374307</t>
+          <t>3440505</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3569871</t>
+          <t>3628996</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3569871</t>
+          <t>3628996</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3569871</t>
+          <t>3628996</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6944178</t>
+          <t>7069502</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6944178</t>
+          <t>7069502</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6944178</t>
+          <t>7069502</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
